--- a/data/source-momento4-planeacion-territorial/Experiencia_ _Transformaciones que nos conectan_. (UC DIGITAL)(1-62).xlsx
+++ b/data/source-momento4-planeacion-territorial/Experiencia_ _Transformaciones que nos conectan_. (UC DIGITAL)(1-62).xlsx
@@ -124,10 +124,10 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -176,10 +176,10 @@
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -496,7 +496,7 @@
         <v>46252.32575231481</v>
       </c>
       <c r="D2" t="str">
-        <v>eeduardoroa@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -525,7 +525,7 @@
         <v>46252.402025462965</v>
       </c>
       <c r="D3" t="str">
-        <v>vnancy@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -554,7 +554,7 @@
         <v>46252.40640046296</v>
       </c>
       <c r="D4" t="str">
-        <v>erpena@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -586,7 +586,7 @@
         <v>46252.40914351852</v>
       </c>
       <c r="D5" t="str">
-        <v>nenriqueacosta@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -615,7 +615,7 @@
         <v>46252.409317129626</v>
       </c>
       <c r="D6" t="str">
-        <v>juandrodriguez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -644,7 +644,7 @@
         <v>46252.40967592593</v>
       </c>
       <c r="D7" t="str">
-        <v>njfranco@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -676,7 +676,7 @@
         <v>46252.41716435185</v>
       </c>
       <c r="D8" t="str">
-        <v>ncrubio@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -699,7 +699,7 @@
         <v>46252.422534722224</v>
       </c>
       <c r="D9" t="str">
-        <v>nestorjgarcia@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -728,7 +728,7 @@
         <v>46252.42417824074</v>
       </c>
       <c r="D10" t="str">
-        <v>hcastrof@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -760,7 +760,7 @@
         <v>46252.42894675926</v>
       </c>
       <c r="D11" t="str">
-        <v>nxsanchez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -789,7 +789,7 @@
         <v>46252.42957175926</v>
       </c>
       <c r="D12" t="str">
-        <v>sfvergara@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -821,7 +821,7 @@
         <v>46252.430231481485</v>
       </c>
       <c r="D13" t="str">
-        <v>dfpachon@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -853,7 +853,7 @@
         <v>46252.43145833333</v>
       </c>
       <c r="D14" t="str">
-        <v>smurciac@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -885,7 +885,7 @@
         <v>46252.43921296296</v>
       </c>
       <c r="D15" t="str">
-        <v>rmunevar@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -917,7 +917,7 @@
         <v>46252.439479166664</v>
       </c>
       <c r="D16" t="str">
-        <v>clorenarodriguez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -949,7 +949,7 @@
         <v>46252.6472337963</v>
       </c>
       <c r="D17" t="str">
-        <v>karendortiz@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -981,7 +981,7 @@
         <v>46252.64790509259</v>
       </c>
       <c r="D18" t="str">
-        <v>gtgutierrez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1013,7 +1013,7 @@
         <v>46252.64818287037</v>
       </c>
       <c r="D19" t="str">
-        <v>vballen@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1042,7 +1042,7 @@
         <v>46252.64892361111</v>
       </c>
       <c r="D20" t="str">
-        <v>decasas@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1071,7 +1071,7 @@
         <v>46252.64915509259</v>
       </c>
       <c r="D21" t="str">
-        <v>jcforigua@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1100,7 +1100,7 @@
         <v>46252.64927083333</v>
       </c>
       <c r="D22" t="str">
-        <v>kxvillamil@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>46252.649375</v>
       </c>
       <c r="D23" t="str">
-        <v>dsantiagocasallas@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1158,7 +1158,7 @@
         <v>46252.64938657408</v>
       </c>
       <c r="D24" t="str">
-        <v>krociomurcia@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1190,7 +1190,7 @@
         <v>46252.64939814815</v>
       </c>
       <c r="D25" t="str">
-        <v>kdrodriguezvelosa@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1222,7 +1222,7 @@
         <v>46252.649664351855</v>
       </c>
       <c r="D26" t="str">
-        <v>paulaaperez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1251,7 +1251,7 @@
         <v>46252.65572916667</v>
       </c>
       <c r="D27" t="str">
-        <v>jefersonalejandroramirez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1283,7 +1283,7 @@
         <v>46252.65583333333</v>
       </c>
       <c r="D28" t="str">
-        <v>ypmaldonado@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1312,7 +1312,7 @@
         <v>46252.65650462963</v>
       </c>
       <c r="D29" t="str">
-        <v>yandreyrincon@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1341,7 +1341,7 @@
         <v>46252.65765046296</v>
       </c>
       <c r="D30" t="str">
-        <v>nmhuertas@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1373,7 +1373,7 @@
         <v>46252.65819444445</v>
       </c>
       <c r="D31" t="str">
-        <v>jalayon@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1405,7 +1405,7 @@
         <v>46252.65819444445</v>
       </c>
       <c r="D32" t="str">
-        <v>ndalarcon@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1437,7 +1437,7 @@
         <v>46252.65944444444</v>
       </c>
       <c r="D33" t="str">
-        <v>ljroncancio@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1466,7 +1466,7 @@
         <v>46252.663252314815</v>
       </c>
       <c r="D34" t="str">
-        <v>yessicatrodriguez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1495,7 +1495,7 @@
         <v>46252.663356481484</v>
       </c>
       <c r="D35" t="str">
-        <v>lncajamarca@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1524,7 +1524,7 @@
         <v>46252.66417824074</v>
       </c>
       <c r="D36" t="str">
-        <v>nleonr@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1556,7 +1556,7 @@
         <v>46252.66584490741</v>
       </c>
       <c r="D37" t="str">
-        <v>angiecrojas@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1588,7 +1588,7 @@
         <v>46252.66630787037</v>
       </c>
       <c r="D38" t="str">
-        <v>nalavardo@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>46252.66732638889</v>
       </c>
       <c r="D39" t="str">
-        <v>cristiancpachon@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1649,7 +1649,7 @@
         <v>46252.67229166667</v>
       </c>
       <c r="D40" t="str">
-        <v>yzsantana@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1678,7 +1678,7 @@
         <v>46252.673425925925</v>
       </c>
       <c r="D41" t="str">
-        <v>jprocha@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1710,7 +1710,7 @@
         <v>46252.673472222225</v>
       </c>
       <c r="D42" t="str">
-        <v>vjcastro@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -1742,7 +1742,7 @@
         <v>46252.67359953704</v>
       </c>
       <c r="D43" t="str">
-        <v>kaprada@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -1774,7 +1774,7 @@
         <v>46252.67375</v>
       </c>
       <c r="D44" t="str">
-        <v>hcarolinasierra@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -1806,7 +1806,7 @@
         <v>46252.67398148148</v>
       </c>
       <c r="D45" t="str">
-        <v>rjdelgado@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -1835,7 +1835,7 @@
         <v>46252.680231481485</v>
       </c>
       <c r="D46" t="str">
-        <v>empachon@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -1867,7 +1867,7 @@
         <v>46252.68035879629</v>
       </c>
       <c r="D47" t="str">
-        <v>jcarinagomez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -1896,7 +1896,7 @@
         <v>46252.68325231481</v>
       </c>
       <c r="D48" t="str">
-        <v>hacorredor@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -1928,7 +1928,7 @@
         <v>46252.68340277778</v>
       </c>
       <c r="D49" t="str">
-        <v>ynmolina@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -1960,7 +1960,7 @@
         <v>46252.683483796296</v>
       </c>
       <c r="D50" t="str">
-        <v>jbriseno@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -1992,7 +1992,7 @@
         <v>46252.68378472222</v>
       </c>
       <c r="D51" t="str">
-        <v>mehueso@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2024,7 +2024,7 @@
         <v>46252.683912037035</v>
       </c>
       <c r="D52" t="str">
-        <v>sjanethrincon@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2056,7 +2056,7 @@
         <v>46252.80976851852</v>
       </c>
       <c r="D53" t="str">
-        <v>acamiloramirez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2088,7 +2088,7 @@
         <v>46252.81060185185</v>
       </c>
       <c r="D54" t="str">
-        <v>landrearivera@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2123,7 +2123,7 @@
         <v>46252.81670138889</v>
       </c>
       <c r="D55" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I55" t="str">
         <v>Graduados</v>
@@ -2155,7 +2155,7 @@
         <v>46252.817557870374</v>
       </c>
       <c r="D56" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I56" t="str">
         <v>Creadores de Oportunidades (estudiantes)</v>
@@ -2187,7 +2187,7 @@
         <v>46252.82019675926</v>
       </c>
       <c r="D57" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I57" t="str">
         <v>Graduados</v>
@@ -2219,7 +2219,7 @@
         <v>46252.83131944444</v>
       </c>
       <c r="D58" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I58" t="str">
         <v>Graduados</v>
@@ -2251,7 +2251,7 @@
         <v>46252.84142361111</v>
       </c>
       <c r="D59" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I59" t="str">
         <v>Graduados</v>
@@ -2283,7 +2283,7 @@
         <v>46252.84261574074</v>
       </c>
       <c r="D60" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I60" t="str">
         <v>Graduados</v>
@@ -2315,7 +2315,7 @@
         <v>46252.843819444446</v>
       </c>
       <c r="D61" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I61" t="str">
         <v>Graduados</v>
@@ -2347,7 +2347,7 @@
         <v>46252.84425925926</v>
       </c>
       <c r="D62" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I62" t="str">
         <v>Graduados</v>
@@ -2376,7 +2376,7 @@
         <v>46252.844618055555</v>
       </c>
       <c r="D63" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I63" t="str">
         <v>Graduados</v>
